--- a/PROJECT FILE/KENYA_FLEET_LOGISTICS.xlsx
+++ b/PROJECT FILE/KENYA_FLEET_LOGISTICS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dba8f9a7b601c79e/Documentos/EXCEL DATA ANALYSIS PROJECT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dba8f9a7b601c79e/Documentos/GITHUB REPOSITORIES/KENYA FLEET LOGISTCS ANALYSIS/KENYA-FLEET-LOGISTICS-ANALYSIS/PROJECT FILE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{CA87C4F3-E8AE-4FFF-B7B4-29833746138A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2425BFB5-8DAC-4FE2-B4E9-66CA97189AA9}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{CA87C4F3-E8AE-4FFF-B7B4-29833746138A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE80A332-2B1B-4F16-84BD-737284424740}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fleet Data" sheetId="2" r:id="rId1"/>
@@ -19,12 +19,12 @@
     <sheet name="Delivery Tracker" sheetId="5" r:id="rId4"/>
     <sheet name="Charts &amp; Visuals" sheetId="6" r:id="rId5"/>
     <sheet name="Dashboard" sheetId="7" r:id="rId6"/>
-    <sheet name="README" sheetId="1" r:id="rId7"/>
+    <sheet name="README" sheetId="1" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Purchase Orders'!$A$1:$O$481</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -7895,7 +7895,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8194,6 +8194,12 @@
     <xf numFmtId="3" fontId="16" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8203,22 +8209,34 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="12" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8254,50 +8272,14 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8308,10 +8290,39 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12833,7 +12844,7 @@
   <dimension ref="A1:S201"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" style="55" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" style="55" customWidth="1"/>
     <col min="2" max="2" width="14" style="55" customWidth="1"/>
     <col min="3" max="3" width="13" style="55" customWidth="1"/>
     <col min="4" max="4" width="15" style="55" customWidth="1"/>
@@ -12845,7 +12856,8 @@
     <col min="13" max="13" width="13" style="55" customWidth="1"/>
     <col min="14" max="15" width="14" style="55" customWidth="1"/>
     <col min="16" max="16" width="8.7109375" style="55"/>
-    <col min="17" max="18" width="16" style="55" customWidth="1"/>
+    <col min="17" max="17" width="20.140625" style="55" customWidth="1"/>
+    <col min="18" max="18" width="20.28515625" style="55" customWidth="1"/>
     <col min="19" max="16384" width="8.7109375" style="55"/>
   </cols>
   <sheetData>
@@ -13308,7 +13320,7 @@
       </c>
       <c r="S8" s="57"/>
     </row>
-    <row r="9" spans="1:19" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="74" t="s">
         <v>82</v>
       </c>
@@ -80865,46 +80877,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:24" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="108" t="s">
         <v>2288</v>
       </c>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="111"/>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
     </row>
     <row r="2" spans="2:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="109" t="s">
         <v>2289</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112"/>
-      <c r="H2" s="112"/>
-      <c r="I2" s="112"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="112"/>
-      <c r="L2" s="112"/>
-      <c r="M2" s="112"/>
-      <c r="N2" s="112"/>
-      <c r="O2" s="112"/>
-      <c r="P2" s="112"/>
-      <c r="Q2" s="112"/>
-      <c r="R2" s="112"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="109"/>
+      <c r="K2" s="109"/>
+      <c r="L2" s="109"/>
+      <c r="M2" s="109"/>
+      <c r="N2" s="109"/>
+      <c r="O2" s="109"/>
+      <c r="P2" s="109"/>
+      <c r="Q2" s="109"/>
+      <c r="R2" s="109"/>
       <c r="T2" s="27"/>
       <c r="U2" s="27"/>
     </row>
@@ -80913,10 +80925,10 @@
       <c r="V3" s="26"/>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="O4" s="108" t="s">
+      <c r="O4" s="110" t="s">
         <v>2290</v>
       </c>
-      <c r="P4" s="109"/>
+      <c r="P4" s="111"/>
       <c r="S4" s="25"/>
       <c r="V4" s="26"/>
     </row>
@@ -81047,11 +81059,11 @@
       <c r="X16" s="39"/>
     </row>
     <row r="17" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="O17" s="108" t="s">
+      <c r="O17" s="110" t="s">
         <v>2292</v>
       </c>
-      <c r="P17" s="110"/>
-      <c r="Q17" s="109"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="111"/>
       <c r="S17" s="25"/>
       <c r="W17" s="26"/>
     </row>
@@ -81459,11 +81471,11 @@
       <c r="V43" s="27"/>
     </row>
     <row r="44" spans="2:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O44" s="108" t="s">
+      <c r="O44" s="110" t="s">
         <v>2320</v>
       </c>
-      <c r="P44" s="110"/>
-      <c r="Q44" s="109"/>
+      <c r="P44" s="112"/>
+      <c r="Q44" s="111"/>
       <c r="S44" s="25"/>
       <c r="W44" s="40"/>
       <c r="X44" s="39"/>
@@ -81648,10 +81660,10 @@
       <c r="V56" s="28"/>
     </row>
     <row r="57" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="O57" s="108" t="s">
+      <c r="O57" s="110" t="s">
         <v>2322</v>
       </c>
-      <c r="P57" s="109"/>
+      <c r="P57" s="111"/>
       <c r="T57" s="27"/>
       <c r="U57" s="27"/>
     </row>
@@ -81726,10 +81738,10 @@
       <c r="V64" s="26"/>
     </row>
     <row r="65" spans="15:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O65" s="108" t="s">
+      <c r="O65" s="110" t="s">
         <v>2323</v>
       </c>
-      <c r="P65" s="109"/>
+      <c r="P65" s="111"/>
       <c r="T65" s="41"/>
       <c r="U65" s="41"/>
     </row>
@@ -81864,13 +81876,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="O57:P57"/>
+    <mergeCell ref="O65:P65"/>
     <mergeCell ref="B1:R1"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="O4:P4"/>
     <mergeCell ref="O17:Q17"/>
     <mergeCell ref="O44:Q44"/>
-    <mergeCell ref="O57:P57"/>
-    <mergeCell ref="O65:P65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -81892,141 +81904,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="128" t="s">
+      <c r="B1" s="115" t="s">
         <v>2325</v>
       </c>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="128"/>
-      <c r="J1" s="128"/>
-      <c r="K1" s="128"/>
-      <c r="L1" s="128"/>
-      <c r="M1" s="128"/>
-      <c r="N1" s="128"/>
-      <c r="O1" s="128"/>
-      <c r="P1" s="128"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
     </row>
     <row r="2" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="116" t="s">
         <v>2326</v>
       </c>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="129"/>
-      <c r="K2" s="129"/>
-      <c r="L2" s="129"/>
-      <c r="M2" s="129"/>
-      <c r="N2" s="129"/>
-      <c r="O2" s="129"/>
-      <c r="P2" s="129"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="116"/>
     </row>
     <row r="4" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="130" t="s">
+      <c r="B4" s="117" t="s">
         <v>2327</v>
       </c>
-      <c r="C4" s="130"/>
-      <c r="D4" s="131" t="s">
+      <c r="C4" s="117"/>
+      <c r="D4" s="118" t="s">
         <v>2328</v>
       </c>
-      <c r="E4" s="131"/>
-      <c r="F4" s="132" t="s">
+      <c r="E4" s="118"/>
+      <c r="F4" s="119" t="s">
         <v>2329</v>
       </c>
-      <c r="G4" s="132"/>
-      <c r="H4" s="133" t="s">
+      <c r="G4" s="119"/>
+      <c r="H4" s="120" t="s">
         <v>2330</v>
       </c>
-      <c r="I4" s="133"/>
-      <c r="J4" s="134" t="s">
+      <c r="I4" s="120"/>
+      <c r="J4" s="121" t="s">
         <v>2331</v>
       </c>
-      <c r="K4" s="134"/>
-      <c r="L4" s="135" t="s">
+      <c r="K4" s="121"/>
+      <c r="L4" s="122" t="s">
         <v>2332</v>
       </c>
-      <c r="M4" s="135"/>
+      <c r="M4" s="122"/>
     </row>
     <row r="5" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="111">
+      <c r="B5" s="108">
         <f>'Fleet Data'!R2</f>
         <v>200</v>
       </c>
-      <c r="C5" s="111"/>
-      <c r="D5" s="124">
+      <c r="C5" s="108"/>
+      <c r="D5" s="130">
         <f>'Fleet Data'!R3</f>
         <v>184</v>
       </c>
-      <c r="E5" s="124"/>
-      <c r="F5" s="125">
+      <c r="E5" s="130"/>
+      <c r="F5" s="131">
         <f>'Fleet Data'!R6</f>
         <v>710114919</v>
       </c>
-      <c r="G5" s="125"/>
-      <c r="H5" s="126">
+      <c r="G5" s="131"/>
+      <c r="H5" s="132">
         <f>'Fleet Data'!R7</f>
         <v>68.373500000000035</v>
       </c>
-      <c r="I5" s="126"/>
-      <c r="J5" s="127">
+      <c r="I5" s="132"/>
+      <c r="J5" s="133">
         <f>COUNTA('Purchase Orders'!A2:A481)</f>
         <v>480</v>
       </c>
-      <c r="K5" s="127"/>
-      <c r="L5" s="117">
+      <c r="K5" s="133"/>
+      <c r="L5" s="123">
         <f>COUNTIF('Purchase Orders'!O2:O481,"YES")/COUNTA('Purchase Orders'!O2:O481)*100</f>
         <v>54.374999999999993</v>
       </c>
-      <c r="M5" s="117"/>
+      <c r="M5" s="123"/>
     </row>
     <row r="6" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="118" t="s">
+      <c r="B6" s="124" t="s">
         <v>2333</v>
       </c>
-      <c r="C6" s="118"/>
-      <c r="D6" s="119" t="s">
+      <c r="C6" s="124"/>
+      <c r="D6" s="125" t="s">
         <v>2333</v>
       </c>
-      <c r="E6" s="119"/>
-      <c r="F6" s="120" t="s">
+      <c r="E6" s="125"/>
+      <c r="F6" s="126" t="s">
         <v>2334</v>
       </c>
-      <c r="G6" s="120"/>
-      <c r="H6" s="121" t="s">
+      <c r="G6" s="126"/>
+      <c r="H6" s="127" t="s">
         <v>2335</v>
       </c>
-      <c r="I6" s="121"/>
-      <c r="J6" s="122" t="s">
+      <c r="I6" s="127"/>
+      <c r="J6" s="128" t="s">
         <v>2336</v>
       </c>
-      <c r="K6" s="122"/>
-      <c r="L6" s="123" t="s">
+      <c r="K6" s="128"/>
+      <c r="L6" s="129" t="s">
         <v>2335</v>
       </c>
-      <c r="M6" s="123"/>
+      <c r="M6" s="129"/>
     </row>
     <row r="8" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="115" t="s">
+      <c r="B8" s="134" t="s">
         <v>2337</v>
       </c>
-      <c r="C8" s="115"/>
-      <c r="D8" s="115"/>
-      <c r="E8" s="115"/>
-      <c r="G8" s="115" t="s">
+      <c r="C8" s="134"/>
+      <c r="D8" s="134"/>
+      <c r="E8" s="134"/>
+      <c r="G8" s="147" t="s">
         <v>2338</v>
       </c>
-      <c r="H8" s="115"/>
-      <c r="I8" s="115"/>
-      <c r="J8" s="115"/>
-      <c r="K8" s="115"/>
+      <c r="H8" s="148"/>
+      <c r="I8" s="148"/>
+      <c r="J8" s="149"/>
+      <c r="K8" s="150"/>
     </row>
     <row r="9" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
@@ -82300,19 +82312,19 @@
       </c>
     </row>
     <row r="22" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="115" t="s">
+      <c r="B22" s="134" t="s">
         <v>2342</v>
       </c>
-      <c r="C22" s="115"/>
-      <c r="D22" s="115"/>
-      <c r="E22" s="115"/>
-      <c r="G22" s="115" t="s">
+      <c r="C22" s="134"/>
+      <c r="D22" s="134"/>
+      <c r="E22" s="134"/>
+      <c r="G22" s="134" t="s">
         <v>2343</v>
       </c>
-      <c r="H22" s="115"/>
-      <c r="I22" s="115"/>
-      <c r="J22" s="115"/>
-      <c r="K22" s="115"/>
+      <c r="H22" s="134"/>
+      <c r="I22" s="134"/>
+      <c r="J22" s="134"/>
+      <c r="K22" s="134"/>
     </row>
     <row r="23" spans="2:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
@@ -82704,99 +82716,101 @@
       </c>
     </row>
     <row r="35" spans="2:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="116" t="s">
+      <c r="B35" s="135" t="s">
         <v>2350</v>
       </c>
-      <c r="C35" s="116"/>
-      <c r="D35" s="116"/>
-      <c r="E35" s="116"/>
-      <c r="F35" s="116"/>
-      <c r="G35" s="116"/>
-      <c r="H35" s="116"/>
-      <c r="I35" s="116"/>
-      <c r="J35" s="116"/>
-      <c r="K35" s="116"/>
-    </row>
-    <row r="36" spans="2:11" s="147" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="146" t="s">
+      <c r="C35" s="135"/>
+      <c r="D35" s="135"/>
+      <c r="E35" s="135"/>
+      <c r="F35" s="135"/>
+      <c r="G35" s="135"/>
+      <c r="H35" s="135"/>
+      <c r="I35" s="135"/>
+      <c r="J35" s="135"/>
+      <c r="K35" s="135"/>
+    </row>
+    <row r="36" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="136" t="s">
         <v>2351</v>
       </c>
-      <c r="C36" s="146"/>
-      <c r="D36" s="146"/>
-      <c r="E36" s="146"/>
-      <c r="F36" s="146"/>
-      <c r="G36" s="146"/>
-      <c r="H36" s="146"/>
-      <c r="I36" s="146"/>
-      <c r="J36" s="146"/>
-      <c r="K36" s="146"/>
-    </row>
-    <row r="37" spans="2:11" s="147" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="146" t="s">
+      <c r="C36" s="136"/>
+      <c r="D36" s="136"/>
+      <c r="E36" s="136"/>
+      <c r="F36" s="136"/>
+      <c r="G36" s="136"/>
+      <c r="H36" s="136"/>
+      <c r="I36" s="136"/>
+      <c r="J36" s="136"/>
+      <c r="K36" s="136"/>
+    </row>
+    <row r="37" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="136" t="s">
         <v>2352</v>
       </c>
-      <c r="C37" s="146"/>
-      <c r="D37" s="146"/>
-      <c r="E37" s="146"/>
-      <c r="F37" s="146"/>
-      <c r="G37" s="146"/>
-      <c r="H37" s="146"/>
-      <c r="I37" s="146"/>
-      <c r="J37" s="146"/>
-      <c r="K37" s="146"/>
-    </row>
-    <row r="38" spans="2:11" s="147" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="146" t="s">
+      <c r="C37" s="136"/>
+      <c r="D37" s="136"/>
+      <c r="E37" s="136"/>
+      <c r="F37" s="136"/>
+      <c r="G37" s="136"/>
+      <c r="H37" s="136"/>
+      <c r="I37" s="136"/>
+      <c r="J37" s="136"/>
+      <c r="K37" s="136"/>
+    </row>
+    <row r="38" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="136" t="s">
         <v>2353</v>
       </c>
-      <c r="C38" s="146"/>
-      <c r="D38" s="146"/>
-      <c r="E38" s="146"/>
-      <c r="F38" s="146"/>
-      <c r="G38" s="146"/>
-      <c r="H38" s="146"/>
-      <c r="I38" s="146"/>
-      <c r="J38" s="146"/>
-      <c r="K38" s="146"/>
-    </row>
-    <row r="39" spans="2:11" s="147" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="146" t="s">
+      <c r="C38" s="136"/>
+      <c r="D38" s="136"/>
+      <c r="E38" s="136"/>
+      <c r="F38" s="136"/>
+      <c r="G38" s="136"/>
+      <c r="H38" s="136"/>
+      <c r="I38" s="136"/>
+      <c r="J38" s="136"/>
+      <c r="K38" s="136"/>
+    </row>
+    <row r="39" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="136" t="s">
         <v>2354</v>
       </c>
-      <c r="C39" s="146"/>
-      <c r="D39" s="146"/>
-      <c r="E39" s="146"/>
-      <c r="F39" s="146"/>
-      <c r="G39" s="146"/>
-      <c r="H39" s="146"/>
-      <c r="I39" s="146"/>
-      <c r="J39" s="146"/>
-      <c r="K39" s="146"/>
-    </row>
-    <row r="40" spans="2:11" s="147" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="146" t="s">
+      <c r="C39" s="136"/>
+      <c r="D39" s="136"/>
+      <c r="E39" s="136"/>
+      <c r="F39" s="136"/>
+      <c r="G39" s="136"/>
+      <c r="H39" s="136"/>
+      <c r="I39" s="136"/>
+      <c r="J39" s="136"/>
+      <c r="K39" s="136"/>
+    </row>
+    <row r="40" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="136" t="s">
         <v>2355</v>
       </c>
-      <c r="C40" s="146"/>
-      <c r="D40" s="146"/>
-      <c r="E40" s="146"/>
-      <c r="F40" s="146"/>
-      <c r="G40" s="146"/>
-      <c r="H40" s="146"/>
-      <c r="I40" s="146"/>
-      <c r="J40" s="146"/>
-      <c r="K40" s="146"/>
+      <c r="C40" s="136"/>
+      <c r="D40" s="136"/>
+      <c r="E40" s="136"/>
+      <c r="F40" s="136"/>
+      <c r="G40" s="136"/>
+      <c r="H40" s="136"/>
+      <c r="I40" s="136"/>
+      <c r="J40" s="136"/>
+      <c r="K40" s="136"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="B2:P2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="B36:K36"/>
+    <mergeCell ref="B37:K37"/>
+    <mergeCell ref="B38:K38"/>
+    <mergeCell ref="B39:K39"/>
+    <mergeCell ref="B40:K40"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="G22:K22"/>
+    <mergeCell ref="B35:K35"/>
+    <mergeCell ref="G8:J8"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:E6"/>
@@ -82809,16 +82823,14 @@
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="G8:K8"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="G22:K22"/>
-    <mergeCell ref="B35:K35"/>
-    <mergeCell ref="B36:K36"/>
-    <mergeCell ref="B37:K37"/>
-    <mergeCell ref="B38:K38"/>
-    <mergeCell ref="B39:K39"/>
-    <mergeCell ref="B40:K40"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -82836,150 +82848,150 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="143" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="143"/>
-      <c r="K2" s="143"/>
+      <c r="B2" s="137" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
+      <c r="G2" s="137"/>
+      <c r="H2" s="137"/>
+      <c r="I2" s="137"/>
+      <c r="J2" s="137"/>
+      <c r="K2" s="137"/>
     </row>
     <row r="3" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="143"/>
-      <c r="C3" s="143"/>
-      <c r="D3" s="143"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="143"/>
-      <c r="G3" s="143"/>
-      <c r="H3" s="143"/>
-      <c r="I3" s="143"/>
-      <c r="J3" s="143"/>
-      <c r="K3" s="143"/>
+      <c r="B3" s="137"/>
+      <c r="C3" s="137"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="137"/>
+      <c r="H3" s="137"/>
+      <c r="I3" s="137"/>
+      <c r="J3" s="137"/>
+      <c r="K3" s="137"/>
     </row>
     <row r="4" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="143"/>
-      <c r="C4" s="143"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="143"/>
-      <c r="F4" s="143"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="143"/>
-      <c r="I4" s="143"/>
-      <c r="J4" s="143"/>
-      <c r="K4" s="143"/>
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137"/>
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
     </row>
     <row r="5" spans="2:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="144" t="s">
+      <c r="B5" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="144"/>
-      <c r="D5" s="144"/>
-      <c r="E5" s="144"/>
-      <c r="F5" s="144"/>
-      <c r="G5" s="144"/>
-      <c r="H5" s="144"/>
-      <c r="I5" s="144"/>
-      <c r="J5" s="144"/>
-      <c r="K5" s="144"/>
+      <c r="C5" s="138"/>
+      <c r="D5" s="138"/>
+      <c r="E5" s="138"/>
+      <c r="F5" s="138"/>
+      <c r="G5" s="138"/>
+      <c r="H5" s="138"/>
+      <c r="I5" s="138"/>
+      <c r="J5" s="138"/>
+      <c r="K5" s="138"/>
     </row>
     <row r="6" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="145" t="s">
+      <c r="B6" s="139" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="145"/>
-      <c r="D6" s="145"/>
-      <c r="E6" s="145"/>
-      <c r="F6" s="145"/>
-      <c r="G6" s="145"/>
-      <c r="H6" s="145"/>
-      <c r="I6" s="145"/>
-      <c r="J6" s="145"/>
-      <c r="K6" s="145"/>
+      <c r="C6" s="139"/>
+      <c r="D6" s="139"/>
+      <c r="E6" s="139"/>
+      <c r="F6" s="139"/>
+      <c r="G6" s="139"/>
+      <c r="H6" s="139"/>
+      <c r="I6" s="139"/>
+      <c r="J6" s="139"/>
+      <c r="K6" s="139"/>
     </row>
     <row r="8" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="141" t="s">
+      <c r="B8" s="140" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="141"/>
-      <c r="D8" s="140" t="s">
+      <c r="C8" s="140"/>
+      <c r="D8" s="141" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="140"/>
-      <c r="F8" s="140"/>
-      <c r="G8" s="140"/>
-      <c r="H8" s="140"/>
-      <c r="I8" s="140"/>
-      <c r="J8" s="140"/>
-      <c r="K8" s="140"/>
+      <c r="E8" s="141"/>
+      <c r="F8" s="141"/>
+      <c r="G8" s="141"/>
+      <c r="H8" s="141"/>
+      <c r="I8" s="141"/>
+      <c r="J8" s="141"/>
+      <c r="K8" s="141"/>
     </row>
     <row r="9" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="141" t="s">
+      <c r="B9" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="141"/>
-      <c r="D9" s="140" t="s">
+      <c r="C9" s="140"/>
+      <c r="D9" s="141" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="140"/>
-      <c r="F9" s="140"/>
-      <c r="G9" s="140"/>
-      <c r="H9" s="140"/>
-      <c r="I9" s="140"/>
-      <c r="J9" s="140"/>
-      <c r="K9" s="140"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="141"/>
+      <c r="G9" s="141"/>
+      <c r="H9" s="141"/>
+      <c r="I9" s="141"/>
+      <c r="J9" s="141"/>
+      <c r="K9" s="141"/>
     </row>
     <row r="10" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="141" t="s">
+      <c r="B10" s="140" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="141"/>
-      <c r="D10" s="140" t="s">
+      <c r="C10" s="140"/>
+      <c r="D10" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="140"/>
-      <c r="F10" s="140"/>
-      <c r="G10" s="140"/>
-      <c r="H10" s="140"/>
-      <c r="I10" s="140"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="140"/>
+      <c r="E10" s="141"/>
+      <c r="F10" s="141"/>
+      <c r="G10" s="141"/>
+      <c r="H10" s="141"/>
+      <c r="I10" s="141"/>
+      <c r="J10" s="141"/>
+      <c r="K10" s="141"/>
     </row>
     <row r="11" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="141" t="s">
+      <c r="B11" s="140" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="141"/>
-      <c r="D11" s="140" t="s">
+      <c r="C11" s="140"/>
+      <c r="D11" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="140"/>
-      <c r="F11" s="140"/>
-      <c r="G11" s="140"/>
-      <c r="H11" s="140"/>
-      <c r="I11" s="140"/>
-      <c r="J11" s="140"/>
-      <c r="K11" s="140"/>
+      <c r="E11" s="141"/>
+      <c r="F11" s="141"/>
+      <c r="G11" s="141"/>
+      <c r="H11" s="141"/>
+      <c r="I11" s="141"/>
+      <c r="J11" s="141"/>
+      <c r="K11" s="141"/>
     </row>
     <row r="12" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="141" t="s">
+      <c r="B12" s="140" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="141"/>
-      <c r="D12" s="140" t="s">
+      <c r="C12" s="140"/>
+      <c r="D12" s="141" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="140"/>
-      <c r="F12" s="140"/>
-      <c r="G12" s="140"/>
-      <c r="H12" s="140"/>
-      <c r="I12" s="140"/>
-      <c r="J12" s="140"/>
-      <c r="K12" s="140"/>
+      <c r="E12" s="141"/>
+      <c r="F12" s="141"/>
+      <c r="G12" s="141"/>
+      <c r="H12" s="141"/>
+      <c r="I12" s="141"/>
+      <c r="J12" s="141"/>
+      <c r="K12" s="141"/>
     </row>
     <row r="14" spans="2:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="142" t="s">
@@ -82996,246 +83008,246 @@
       <c r="K14" s="142"/>
     </row>
     <row r="15" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="140" t="s">
+      <c r="B15" s="141" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="140"/>
-      <c r="D15" s="140"/>
-      <c r="E15" s="140"/>
-      <c r="F15" s="140"/>
-      <c r="G15" s="140"/>
-      <c r="H15" s="140"/>
-      <c r="I15" s="140"/>
-      <c r="J15" s="140"/>
-      <c r="K15" s="140"/>
+      <c r="C15" s="141"/>
+      <c r="D15" s="141"/>
+      <c r="E15" s="141"/>
+      <c r="F15" s="141"/>
+      <c r="G15" s="141"/>
+      <c r="H15" s="141"/>
+      <c r="I15" s="141"/>
+      <c r="J15" s="141"/>
+      <c r="K15" s="141"/>
     </row>
     <row r="16" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="138" t="s">
+      <c r="B16" s="143" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="138"/>
-      <c r="D16" s="138"/>
-      <c r="E16" s="138"/>
-      <c r="F16" s="138"/>
-      <c r="G16" s="138"/>
-      <c r="H16" s="138"/>
-      <c r="I16" s="138"/>
-      <c r="J16" s="138"/>
-      <c r="K16" s="138"/>
+      <c r="C16" s="143"/>
+      <c r="D16" s="143"/>
+      <c r="E16" s="143"/>
+      <c r="F16" s="143"/>
+      <c r="G16" s="143"/>
+      <c r="H16" s="143"/>
+      <c r="I16" s="143"/>
+      <c r="J16" s="143"/>
+      <c r="K16" s="143"/>
     </row>
     <row r="17" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="140" t="s">
+      <c r="B17" s="141" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="140"/>
-      <c r="D17" s="140"/>
-      <c r="E17" s="140"/>
-      <c r="F17" s="140"/>
-      <c r="G17" s="140"/>
-      <c r="H17" s="140"/>
-      <c r="I17" s="140"/>
-      <c r="J17" s="140"/>
-      <c r="K17" s="140"/>
+      <c r="C17" s="141"/>
+      <c r="D17" s="141"/>
+      <c r="E17" s="141"/>
+      <c r="F17" s="141"/>
+      <c r="G17" s="141"/>
+      <c r="H17" s="141"/>
+      <c r="I17" s="141"/>
+      <c r="J17" s="141"/>
+      <c r="K17" s="141"/>
     </row>
     <row r="18" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="138" t="s">
+      <c r="B18" s="143" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="138"/>
-      <c r="D18" s="138"/>
-      <c r="E18" s="138"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="138"/>
-      <c r="H18" s="138"/>
-      <c r="I18" s="138"/>
-      <c r="J18" s="138"/>
-      <c r="K18" s="138"/>
+      <c r="C18" s="143"/>
+      <c r="D18" s="143"/>
+      <c r="E18" s="143"/>
+      <c r="F18" s="143"/>
+      <c r="G18" s="143"/>
+      <c r="H18" s="143"/>
+      <c r="I18" s="143"/>
+      <c r="J18" s="143"/>
+      <c r="K18" s="143"/>
     </row>
     <row r="19" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="140" t="s">
+      <c r="B19" s="141" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="140"/>
-      <c r="D19" s="140"/>
-      <c r="E19" s="140"/>
-      <c r="F19" s="140"/>
-      <c r="G19" s="140"/>
-      <c r="H19" s="140"/>
-      <c r="I19" s="140"/>
-      <c r="J19" s="140"/>
-      <c r="K19" s="140"/>
+      <c r="C19" s="141"/>
+      <c r="D19" s="141"/>
+      <c r="E19" s="141"/>
+      <c r="F19" s="141"/>
+      <c r="G19" s="141"/>
+      <c r="H19" s="141"/>
+      <c r="I19" s="141"/>
+      <c r="J19" s="141"/>
+      <c r="K19" s="141"/>
     </row>
     <row r="20" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="138" t="s">
+      <c r="B20" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="138"/>
-      <c r="D20" s="138"/>
-      <c r="E20" s="138"/>
-      <c r="F20" s="138"/>
-      <c r="G20" s="138"/>
-      <c r="H20" s="138"/>
-      <c r="I20" s="138"/>
-      <c r="J20" s="138"/>
-      <c r="K20" s="138"/>
+      <c r="C20" s="143"/>
+      <c r="D20" s="143"/>
+      <c r="E20" s="143"/>
+      <c r="F20" s="143"/>
+      <c r="G20" s="143"/>
+      <c r="H20" s="143"/>
+      <c r="I20" s="143"/>
+      <c r="J20" s="143"/>
+      <c r="K20" s="143"/>
     </row>
     <row r="21" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="140" t="s">
+      <c r="B21" s="141" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="140"/>
-      <c r="D21" s="140"/>
-      <c r="E21" s="140"/>
-      <c r="F21" s="140"/>
-      <c r="G21" s="140"/>
-      <c r="H21" s="140"/>
-      <c r="I21" s="140"/>
-      <c r="J21" s="140"/>
-      <c r="K21" s="140"/>
+      <c r="C21" s="141"/>
+      <c r="D21" s="141"/>
+      <c r="E21" s="141"/>
+      <c r="F21" s="141"/>
+      <c r="G21" s="141"/>
+      <c r="H21" s="141"/>
+      <c r="I21" s="141"/>
+      <c r="J21" s="141"/>
+      <c r="K21" s="141"/>
     </row>
     <row r="22" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="138" t="s">
+      <c r="B22" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="138"/>
-      <c r="D22" s="138"/>
-      <c r="E22" s="138"/>
-      <c r="F22" s="138"/>
-      <c r="G22" s="138"/>
-      <c r="H22" s="138"/>
-      <c r="I22" s="138"/>
-      <c r="J22" s="138"/>
-      <c r="K22" s="138"/>
+      <c r="C22" s="143"/>
+      <c r="D22" s="143"/>
+      <c r="E22" s="143"/>
+      <c r="F22" s="143"/>
+      <c r="G22" s="143"/>
+      <c r="H22" s="143"/>
+      <c r="I22" s="143"/>
+      <c r="J22" s="143"/>
+      <c r="K22" s="143"/>
     </row>
     <row r="24" spans="2:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="139" t="s">
+      <c r="B24" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="139"/>
-      <c r="D24" s="139"/>
-      <c r="E24" s="139"/>
-      <c r="F24" s="139"/>
-      <c r="G24" s="139"/>
-      <c r="H24" s="139"/>
-      <c r="I24" s="139"/>
-      <c r="J24" s="139"/>
-      <c r="K24" s="139"/>
+      <c r="C24" s="144"/>
+      <c r="D24" s="144"/>
+      <c r="E24" s="144"/>
+      <c r="F24" s="144"/>
+      <c r="G24" s="144"/>
+      <c r="H24" s="144"/>
+      <c r="I24" s="144"/>
+      <c r="J24" s="144"/>
+      <c r="K24" s="144"/>
     </row>
     <row r="25" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="136" t="s">
+      <c r="B25" s="145" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="136"/>
-      <c r="D25" s="137" t="s">
+      <c r="C25" s="145"/>
+      <c r="D25" s="146" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="137"/>
-      <c r="F25" s="137"/>
-      <c r="G25" s="137"/>
-      <c r="H25" s="137"/>
-      <c r="I25" s="137"/>
-      <c r="J25" s="137"/>
-      <c r="K25" s="137"/>
+      <c r="E25" s="146"/>
+      <c r="F25" s="146"/>
+      <c r="G25" s="146"/>
+      <c r="H25" s="146"/>
+      <c r="I25" s="146"/>
+      <c r="J25" s="146"/>
+      <c r="K25" s="146"/>
     </row>
     <row r="26" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="136" t="s">
+      <c r="B26" s="145" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="136"/>
-      <c r="D26" s="137" t="s">
+      <c r="C26" s="145"/>
+      <c r="D26" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="E26" s="137"/>
-      <c r="F26" s="137"/>
-      <c r="G26" s="137"/>
-      <c r="H26" s="137"/>
-      <c r="I26" s="137"/>
-      <c r="J26" s="137"/>
-      <c r="K26" s="137"/>
+      <c r="E26" s="146"/>
+      <c r="F26" s="146"/>
+      <c r="G26" s="146"/>
+      <c r="H26" s="146"/>
+      <c r="I26" s="146"/>
+      <c r="J26" s="146"/>
+      <c r="K26" s="146"/>
     </row>
     <row r="27" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="136" t="s">
+      <c r="B27" s="145" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="136"/>
-      <c r="D27" s="137" t="s">
+      <c r="C27" s="145"/>
+      <c r="D27" s="146" t="s">
         <v>28</v>
       </c>
-      <c r="E27" s="137"/>
-      <c r="F27" s="137"/>
-      <c r="G27" s="137"/>
-      <c r="H27" s="137"/>
-      <c r="I27" s="137"/>
-      <c r="J27" s="137"/>
-      <c r="K27" s="137"/>
+      <c r="E27" s="146"/>
+      <c r="F27" s="146"/>
+      <c r="G27" s="146"/>
+      <c r="H27" s="146"/>
+      <c r="I27" s="146"/>
+      <c r="J27" s="146"/>
+      <c r="K27" s="146"/>
     </row>
     <row r="28" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="136" t="s">
+      <c r="B28" s="145" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="136"/>
-      <c r="D28" s="137" t="s">
+      <c r="C28" s="145"/>
+      <c r="D28" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="137"/>
-      <c r="F28" s="137"/>
-      <c r="G28" s="137"/>
-      <c r="H28" s="137"/>
-      <c r="I28" s="137"/>
-      <c r="J28" s="137"/>
-      <c r="K28" s="137"/>
+      <c r="E28" s="146"/>
+      <c r="F28" s="146"/>
+      <c r="G28" s="146"/>
+      <c r="H28" s="146"/>
+      <c r="I28" s="146"/>
+      <c r="J28" s="146"/>
+      <c r="K28" s="146"/>
     </row>
     <row r="29" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="136" t="s">
+      <c r="B29" s="145" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="136"/>
-      <c r="D29" s="137" t="s">
+      <c r="C29" s="145"/>
+      <c r="D29" s="146" t="s">
         <v>32</v>
       </c>
-      <c r="E29" s="137"/>
-      <c r="F29" s="137"/>
-      <c r="G29" s="137"/>
-      <c r="H29" s="137"/>
-      <c r="I29" s="137"/>
-      <c r="J29" s="137"/>
-      <c r="K29" s="137"/>
+      <c r="E29" s="146"/>
+      <c r="F29" s="146"/>
+      <c r="G29" s="146"/>
+      <c r="H29" s="146"/>
+      <c r="I29" s="146"/>
+      <c r="J29" s="146"/>
+      <c r="K29" s="146"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B2:K4"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="B6:K6"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:K8"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:K27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:K28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:K29"/>
+    <mergeCell ref="B22:K22"/>
+    <mergeCell ref="B24:K24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:K25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:K26"/>
+    <mergeCell ref="B17:K17"/>
+    <mergeCell ref="B18:K18"/>
+    <mergeCell ref="B19:K19"/>
+    <mergeCell ref="B20:K20"/>
+    <mergeCell ref="B21:K21"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:K12"/>
+    <mergeCell ref="B14:K14"/>
+    <mergeCell ref="B15:K15"/>
+    <mergeCell ref="B16:K16"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D9:K9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D10:K10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:K11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:K12"/>
-    <mergeCell ref="B14:K14"/>
-    <mergeCell ref="B15:K15"/>
-    <mergeCell ref="B16:K16"/>
-    <mergeCell ref="B17:K17"/>
-    <mergeCell ref="B18:K18"/>
-    <mergeCell ref="B19:K19"/>
-    <mergeCell ref="B20:K20"/>
-    <mergeCell ref="B21:K21"/>
-    <mergeCell ref="B22:K22"/>
-    <mergeCell ref="B24:K24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:K25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:K26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:K27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:K28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:K29"/>
+    <mergeCell ref="B2:K4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="B6:K6"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:K8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
